--- a/output/pdf_financials_xlsx/MDNA.xlsx
+++ b/output/pdf_financials_xlsx/MDNA.xlsx
@@ -6442,7 +6442,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>-</t>
@@ -10430,7 +10434,11 @@
           <t>Prepaids and deposits (Note 6)</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MDNA.xlsx
+++ b/output/pdf_financials_xlsx/MDNA.xlsx
@@ -873,10 +873,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.0328</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003291</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>-0.000102</v>
@@ -1567,10 +1567,10 @@
         <v>-1.334064</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-7.631265</v>
+        <v>-7.598465</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-7.465452</v>
+        <v>-7.462161</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-4.707929</v>
@@ -1651,10 +1651,10 @@
         <v>-1.332629</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-7.624778</v>
+        <v>-7.591978</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-7.455748</v>
+        <v>-7.452457</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-4.701111</v>
@@ -1858,16 +1858,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.847702</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>5.33871</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>14.038115</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>3.938734</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>2.370976</v>
@@ -1938,16 +1938,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.847702</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>5.33871</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>14.038115</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>3.938734</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>2.370976</v>
@@ -2436,16 +2436,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.847702</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>5.643328</v>
+        <v>0.304618</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>14.25194</v>
+        <v>0.213825</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>4.125842</v>
+        <v>0.187108</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>2.702708</v>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
@@ -19095,7 +19095,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -19521,7 +19521,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">

--- a/output/pdf_financials_xlsx/MDNA.xlsx
+++ b/output/pdf_financials_xlsx/MDNA.xlsx
@@ -528,10 +528,8 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -570,10 +568,8 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -612,10 +608,8 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -654,10 +648,8 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.031418</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0</v>
@@ -696,10 +688,8 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>0.771408</v>
@@ -738,10 +728,8 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>0</v>
@@ -780,10 +768,8 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0.202682</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>1.199664</v>
@@ -822,10 +808,8 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-0.202682</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-1.199664</v>
@@ -864,10 +848,8 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -906,10 +888,8 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>-0</v>
@@ -948,10 +928,8 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>0</v>
@@ -990,10 +968,8 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>0.133959</v>
@@ -1032,10 +1008,8 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-0.202682</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-1.334064</v>
@@ -1074,10 +1048,8 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0</v>
@@ -1240,10 +1212,8 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-0.202682</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-1.334064</v>
@@ -1282,10 +1252,8 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>0</v>
@@ -1324,10 +1292,8 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C22" s="3" t="n">
         <v>0</v>
@@ -1366,10 +1332,8 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-0.202682</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-1.334064</v>
@@ -1558,10 +1522,8 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-0.202682</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-1.334064</v>
@@ -1600,10 +1562,8 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>0.001435</v>
@@ -1642,10 +1602,8 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-0.202682</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-1.332629</v>
@@ -1746,10 +1704,8 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -3164,39 +3120,37 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.006151</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.359376</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.486786</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.8773</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.802025</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>0.456</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>2.245</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>1.672</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>1.617</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>2.701</v>
       </c>
     </row>
     <row r="65">
@@ -3290,39 +3244,37 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.246162</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.91283</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.998486</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.594414</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>1.324</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>1.828</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.949</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>2.183</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.793</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>1.685</v>
       </c>
     </row>
     <row r="68">
@@ -4670,10 +4622,8 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-0.202682</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-1.334064</v>
@@ -4712,10 +4662,8 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
         <v>0</v>
@@ -4754,10 +4702,8 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>0</v>
@@ -4796,10 +4742,8 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C102" s="3" t="n">
         <v>0</v>
@@ -4838,10 +4782,8 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C103" s="3" t="n">
         <v>0</v>
@@ -4880,10 +4822,8 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0.013651</v>
       </c>
       <c r="C104" s="3" t="n">
         <v>0.313671</v>
@@ -4922,10 +4862,8 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C105" s="3" t="n">
         <v>0</v>
@@ -4964,10 +4902,8 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>-0.049096</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>-2.570915</v>
@@ -5006,10 +4942,8 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0.135</v>
       </c>
       <c r="C107" s="3" t="n">
         <v>0</v>
@@ -5048,10 +4982,8 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C108" s="3" t="n">
         <v>0</v>
@@ -5090,10 +5022,8 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C109" s="3" t="n">
         <v>0</v>
@@ -5132,10 +5062,8 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
         <v>0</v>
@@ -5174,10 +5102,8 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -5216,10 +5142,8 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
@@ -5258,10 +5182,8 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C113" s="3" t="n">
         <v>0</v>
@@ -5300,10 +5222,8 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>0</v>
@@ -5318,7 +5238,7 @@
         <v>0</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="H114" s="3" t="n">
         <v>0</v>
@@ -5342,10 +5262,8 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -5384,10 +5302,8 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
         <v>0</v>
@@ -5426,10 +5342,8 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C117" s="3" t="n">
         <v>0</v>
@@ -5468,10 +5382,8 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>0</v>
@@ -5558,10 +5470,8 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C120" s="3" t="n">
         <v>0</v>
@@ -5600,10 +5510,8 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>0</v>
@@ -5642,10 +5550,8 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C122" s="3" t="n">
         <v>0</v>
@@ -5684,10 +5590,8 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C123" s="3" t="n">
         <v>0</v>
@@ -5726,10 +5630,8 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
         <v>0</v>
@@ -5768,10 +5670,8 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>0</v>
@@ -5810,10 +5710,8 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C126" s="3" t="n">
         <v>0</v>
@@ -5914,10 +5812,8 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C128" s="3" t="n">
         <v>0</v>
@@ -6002,10 +5898,8 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C130" s="3" t="n">
         <v>0.125565</v>
@@ -6044,10 +5938,8 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C131" s="3" t="n">
         <v>-0.067671</v>
@@ -6086,10 +5978,8 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>0.847702</v>
       </c>
       <c r="C132" s="3" t="n">
         <v>5.280816</v>
@@ -6128,10 +6018,8 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.847702</v>
       </c>
       <c r="C133" s="3" t="n">
         <v>5.33871</v>
@@ -6170,10 +6058,8 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -6267,7 +6153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O195"/>
+  <dimension ref="A1:O212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -15271,7 +15157,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -16796,28 +16686,26 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>General and administration (Note 18)</t>
+          <t>Net loss for the period $</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="n">
+        <v>-0.202682</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16859,38 +16747,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N154" s="5" t="n">
-        <v>7.874</v>
-      </c>
-      <c r="O154" s="5" t="n">
-        <v>5.962</v>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Item not affecting cash</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Research and development (Note 18)</t>
+          <t>Stock based compensation</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>ResearchAndDevelopment</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="n">
+        <v>0.135</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16932,95 +16822,111 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N155" s="5" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="O155" s="5" t="n">
-        <v>14.444</v>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Net changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Total operating expenses</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F156" s="5" t="n">
-        <v>1.199664</v>
-      </c>
-      <c r="G156" s="5" t="n">
-        <v>5.913781</v>
-      </c>
-      <c r="H156" s="5" t="n">
-        <v>7.42483</v>
-      </c>
-      <c r="I156" s="5" t="n">
-        <v>4.727283</v>
-      </c>
-      <c r="J156" s="5" t="n">
-        <v>8.244999999999999</v>
-      </c>
-      <c r="K156" s="5" t="n">
-        <v>17.395</v>
-      </c>
-      <c r="L156" s="5" t="n">
-        <v>22.473</v>
-      </c>
-      <c r="M156" s="5" t="n">
-        <v>16.303</v>
-      </c>
-      <c r="N156" s="5" t="n">
-        <v>18.674</v>
-      </c>
-      <c r="O156" s="5" t="n">
-        <v>20.406</v>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E156" s="5" t="n">
+        <v>0.013651</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Net changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Finance income</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Due to a director and officer</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" s="5" t="n">
+        <v>0.004935</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17037,11 +16943,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I157" s="5" t="n">
-        <v>-0.000102</v>
-      </c>
-      <c r="J157" s="5" t="n">
-        <v>-0.006727</v>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
@@ -17053,37 +16963,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M157" s="5" t="n">
-        <v>-0.914</v>
-      </c>
-      <c r="N157" s="5" t="n">
-        <v>-1.198</v>
-      </c>
-      <c r="O157" s="5" t="n">
-        <v>-1.35</v>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Net changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Change in fair value of warrant derivative (Note 14)</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net changes in non-cash working capital total</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="n">
+        <v>-0.049096</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17125,38 +17043,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N158" s="5" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="O158" s="5" t="n">
-        <v>-6.347</v>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Foreign exchange (gain) loss</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net proceeds on issuance of common stock</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" s="5" t="n">
+        <v>0.896798</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17168,107 +17084,141 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H159" s="5" t="n">
-        <v>0.043913</v>
-      </c>
-      <c r="I159" s="5" t="n">
-        <v>-0.01915</v>
-      </c>
-      <c r="J159" s="5" t="n">
-        <v>0.038997</v>
-      </c>
-      <c r="K159" s="5" t="n">
-        <v>0.208</v>
-      </c>
-      <c r="L159" s="5" t="n">
-        <v>0.173</v>
-      </c>
-      <c r="M159" s="5" t="n">
-        <v>-1.646</v>
-      </c>
-      <c r="N159" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="O159" s="5" t="n">
-        <v>-0.904</v>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Operating expenses total</t>
+          <t>Net change in cash during the period $</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F160" s="5" t="n">
-        <v>0.1344</v>
-      </c>
-      <c r="G160" s="5" t="n">
-        <v>1.717484</v>
-      </c>
-      <c r="H160" s="5" t="n">
-        <v>0.040622</v>
-      </c>
-      <c r="I160" s="5" t="n">
-        <v>0.019252</v>
-      </c>
-      <c r="J160" s="5" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="K160" s="5" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="L160" s="5" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="M160" s="5" t="n">
-        <v>6.255</v>
-      </c>
-      <c r="N160" s="5" t="n">
-        <v>6.792</v>
-      </c>
-      <c r="O160" s="5" t="n">
-        <v>8.601000000000001</v>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="n">
+        <v>0.847702</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Net loss for the period</t>
+          <t>Cash, beginning of period $</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -17281,11 +17231,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G161" s="5" t="n">
-        <v>-7.631265</v>
-      </c>
-      <c r="H161" s="5" t="n">
-        <v>-7.465452</v>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -17312,34 +17266,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N161" s="5" t="n">
-        <v>-25.466</v>
-      </c>
-      <c r="O161" s="5" t="n">
-        <v>-11.805</v>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Cumulative translation adjustment</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, end of period $</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="n">
+        <v>0.847702</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17361,23 +17321,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J162" s="5" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="K162" s="5" t="n">
-        <v>-0.014</v>
-      </c>
-      <c r="L162" s="5" t="n">
-        <v>-0.063</v>
-      </c>
-      <c r="M162" s="5" t="n">
-        <v>-0.114</v>
-      </c>
-      <c r="N162" s="5" t="n">
-        <v>-0.038</v>
-      </c>
-      <c r="O162" s="5" t="n">
-        <v>-0.016</v>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="163">
@@ -17393,12 +17365,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year</t>
+          <t>General and administration (Note 18)</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -17416,29 +17388,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H163" s="5" t="n">
-        <v>-7.528773</v>
-      </c>
-      <c r="I163" s="5" t="n">
-        <v>-4.701775</v>
-      </c>
-      <c r="J163" s="5" t="n">
-        <v>-8.186</v>
-      </c>
-      <c r="K163" s="5" t="n">
-        <v>-17.303</v>
-      </c>
-      <c r="L163" s="5" t="n">
-        <v>-22.64</v>
-      </c>
-      <c r="M163" s="5" t="n">
-        <v>-10.162</v>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N163" s="5" t="n">
-        <v>-25.504</v>
+        <v>7.874</v>
       </c>
       <c r="O163" s="5" t="n">
-        <v>-11.821</v>
+        <v>5.962</v>
       </c>
     </row>
     <row r="164">
@@ -17454,12 +17438,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share</t>
+          <t>Research and development (Note 18)</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>ResearchAndDevelopment</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -17467,14 +17451,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F164" s="5" t="n">
-        <v>-8e-08</v>
-      </c>
-      <c r="G164" s="5" t="n">
-        <v>-4.5e-07</v>
-      </c>
-      <c r="H164" s="5" t="n">
-        <v>-3e-07</v>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -17496,14 +17486,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M164" s="5" t="n">
-        <v>-1.6e-07</v>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N164" s="5" t="n">
-        <v>-3.7e-07</v>
+        <v>10.8</v>
       </c>
       <c r="O164" s="5" t="n">
-        <v>-1.5e-07</v>
+        <v>14.444</v>
       </c>
     </row>
     <row r="165">
@@ -17514,17 +17506,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Weighted average shares</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Weighted average shares outstanding (Note 11)</t>
+          <t>Total operating expenses</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -17532,51 +17524,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F165" s="5" t="n">
+        <v>1.199664</v>
+      </c>
+      <c r="G165" s="5" t="n">
+        <v>5.913781</v>
+      </c>
+      <c r="H165" s="5" t="n">
+        <v>7.42483</v>
+      </c>
+      <c r="I165" s="5" t="n">
+        <v>4.727283</v>
+      </c>
+      <c r="J165" s="5" t="n">
+        <v>8.244999999999999</v>
+      </c>
+      <c r="K165" s="5" t="n">
+        <v>17.395</v>
+      </c>
+      <c r="L165" s="5" t="n">
+        <v>22.473</v>
+      </c>
+      <c r="M165" s="5" t="n">
+        <v>16.303</v>
       </c>
       <c r="N165" s="5" t="n">
-        <v>69.637469</v>
+        <v>18.674</v>
       </c>
       <c r="O165" s="5" t="n">
-        <v>76.67117500000001</v>
+        <v>20.406</v>
       </c>
     </row>
     <row r="166">
@@ -17592,12 +17568,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>General and administration (Note 17)</t>
+          <t>Finance income</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -17620,32 +17596,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K166" s="5" t="n">
-        <v>6.525</v>
-      </c>
-      <c r="L166" s="5" t="n">
-        <v>7.757</v>
+      <c r="I166" s="5" t="n">
+        <v>-0.000102</v>
+      </c>
+      <c r="J166" s="5" t="n">
+        <v>-0.006727</v>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M166" s="5" t="n">
-        <v>6.999</v>
+        <v>-0.914</v>
       </c>
       <c r="N166" s="5" t="n">
-        <v>7.874</v>
-      </c>
-      <c r="O166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.198</v>
+      </c>
+      <c r="O166" s="5" t="n">
+        <v>-1.35</v>
       </c>
     </row>
     <row r="167">
@@ -17661,14 +17635,10 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Research and development (Note 17)</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>ResearchAndDevelopment</t>
-        </is>
-      </c>
+          <t>Change in fair value of warrant derivative (Note 14)</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -17699,22 +17669,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K167" s="5" t="n">
-        <v>10.87</v>
-      </c>
-      <c r="L167" s="5" t="n">
-        <v>14.716</v>
-      </c>
-      <c r="M167" s="5" t="n">
-        <v>9.304</v>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N167" s="5" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="O167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.92</v>
+      </c>
+      <c r="O167" s="5" t="n">
+        <v>-6.347</v>
       </c>
     </row>
     <row r="168">
@@ -17730,10 +17704,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Transaction costs on derivative warrant liability (Note 12)</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr"/>
+          <t>Foreign exchange (gain) loss</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -17749,43 +17727,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H168" s="5" t="n">
+        <v>0.043913</v>
+      </c>
+      <c r="I168" s="5" t="n">
+        <v>-0.01915</v>
+      </c>
+      <c r="J168" s="5" t="n">
+        <v>0.038997</v>
+      </c>
+      <c r="K168" s="5" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="L168" s="5" t="n">
+        <v>0.173</v>
       </c>
       <c r="M168" s="5" t="n">
-        <v>0.652</v>
-      </c>
-      <c r="N168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.646</v>
+      </c>
+      <c r="N168" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="O168" s="5" t="n">
+        <v>-0.904</v>
       </c>
     </row>
     <row r="169">
@@ -17801,60 +17765,48 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Change in fair value of warrant derivative (Note 12)</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr"/>
+          <t>Operating expenses total</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F169" s="5" t="n">
+        <v>0.1344</v>
+      </c>
+      <c r="G169" s="5" t="n">
+        <v>1.717484</v>
+      </c>
+      <c r="H169" s="5" t="n">
+        <v>0.040622</v>
+      </c>
+      <c r="I169" s="5" t="n">
+        <v>0.019252</v>
+      </c>
+      <c r="J169" s="5" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="K169" s="5" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="L169" s="5" t="n">
+        <v>0.104</v>
       </c>
       <c r="M169" s="5" t="n">
-        <v>-4.347</v>
+        <v>6.255</v>
       </c>
       <c r="N169" s="5" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="O169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.792</v>
+      </c>
+      <c r="O169" s="5" t="n">
+        <v>8.601000000000001</v>
       </c>
     </row>
     <row r="170">
@@ -17870,12 +17822,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Foreign exchange loss (gain)</t>
+          <t>Net loss for the period</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -17889,10 +17841,10 @@
         </is>
       </c>
       <c r="G170" s="5" t="n">
-        <v>-0.03413</v>
+        <v>-7.631265</v>
       </c>
       <c r="H170" s="5" t="n">
-        <v>0.043913</v>
+        <v>-7.465452</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
@@ -17914,16 +17866,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M170" s="5" t="n">
-        <v>-1.646</v>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N170" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="O170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-25.466</v>
+      </c>
+      <c r="O170" s="5" t="n">
+        <v>-11.805</v>
       </c>
     </row>
     <row r="171">
@@ -17939,50 +17891,52 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Cumulative translation adjustment</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F171" s="5" t="n">
-        <v>-1.334064</v>
-      </c>
-      <c r="G171" s="5" t="n">
-        <v>-7.631265</v>
-      </c>
-      <c r="H171" s="5" t="n">
-        <v>-7.465452</v>
-      </c>
-      <c r="I171" s="5" t="n">
-        <v>-4.708031</v>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J171" s="5" t="n">
-        <v>-8.276999999999999</v>
+        <v>0.091</v>
       </c>
       <c r="K171" s="5" t="n">
-        <v>-17.289</v>
+        <v>-0.014</v>
       </c>
       <c r="L171" s="5" t="n">
-        <v>-22.577</v>
+        <v>-0.063</v>
       </c>
       <c r="M171" s="5" t="n">
-        <v>-10.048</v>
+        <v>-0.114</v>
       </c>
       <c r="N171" s="5" t="n">
-        <v>-25.466</v>
-      </c>
-      <c r="O171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.038</v>
+      </c>
+      <c r="O171" s="5" t="n">
+        <v>-0.016</v>
       </c>
     </row>
     <row r="172">
@@ -17993,17 +17947,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Weighted average shares</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Weighted average shares outstanding (Note 9)</t>
+          <t>Comprehensive loss for the year</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -18021,41 +17975,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H172" s="5" t="n">
+        <v>-7.528773</v>
+      </c>
+      <c r="I172" s="5" t="n">
+        <v>-4.701775</v>
+      </c>
+      <c r="J172" s="5" t="n">
+        <v>-8.186</v>
+      </c>
+      <c r="K172" s="5" t="n">
+        <v>-17.303</v>
+      </c>
+      <c r="L172" s="5" t="n">
+        <v>-22.64</v>
       </c>
       <c r="M172" s="5" t="n">
-        <v>64.736493</v>
+        <v>-10.162</v>
       </c>
       <c r="N172" s="5" t="n">
-        <v>69.637469</v>
-      </c>
-      <c r="O172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-25.504</v>
+      </c>
+      <c r="O172" s="5" t="n">
+        <v>-11.821</v>
       </c>
     </row>
     <row r="173">
@@ -18071,12 +18013,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Finance income (Note 2d)</t>
+          <t>Basic and diluted loss per share</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -18084,47 +18026,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F173" s="5" t="n">
+        <v>-8e-08</v>
+      </c>
+      <c r="G173" s="5" t="n">
+        <v>-4.5e-07</v>
+      </c>
+      <c r="H173" s="5" t="n">
+        <v>-3e-07</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J173" s="5" t="n">
-        <v>-0.007</v>
-      </c>
-      <c r="K173" s="5" t="n">
-        <v>-0.314</v>
-      </c>
-      <c r="L173" s="5" t="n">
-        <v>-0.06900000000000001</v>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M173" s="5" t="n">
-        <v>-0.914</v>
-      </c>
-      <c r="N173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.6e-07</v>
+      </c>
+      <c r="N173" s="5" t="n">
+        <v>-3.7e-07</v>
+      </c>
+      <c r="O173" s="5" t="n">
+        <v>-1.5e-07</v>
       </c>
     </row>
     <row r="174">
@@ -18135,15 +18073,19 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Weighted average shares</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Transaction costs on derivative warrant liability</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
+          <t>Weighted average shares outstanding (Note 11)</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -18184,18 +18126,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M174" s="5" t="n">
-        <v>0.652</v>
-      </c>
-      <c r="N174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N174" s="5" t="n">
+        <v>69.637469</v>
+      </c>
+      <c r="O174" s="5" t="n">
+        <v>76.67117500000001</v>
       </c>
     </row>
     <row r="175">
@@ -18211,10 +18151,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share for the year</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
+          <t>General and administration (Note 17)</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -18230,28 +18174,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H175" s="5" t="n">
-        <v>-3.1e-07</v>
-      </c>
-      <c r="I175" s="5" t="n">
-        <v>-1.8e-07</v>
-      </c>
-      <c r="J175" s="5" t="n">
-        <v>-2.6e-07</v>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K175" s="5" t="n">
-        <v>-3.5e-07</v>
+        <v>6.525</v>
       </c>
       <c r="L175" s="5" t="n">
-        <v>-4.2e-07</v>
+        <v>7.757</v>
       </c>
       <c r="M175" s="5" t="n">
-        <v>-1.6e-07</v>
-      </c>
-      <c r="N175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.999</v>
+      </c>
+      <c r="N175" s="5" t="n">
+        <v>7.874</v>
       </c>
       <c r="O175" t="inlineStr">
         <is>
@@ -18272,12 +18220,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding (Note 9)</t>
+          <t>Research and development (Note 17)</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>ResearchAndDevelopment</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -18311,18 +18259,16 @@
         </is>
       </c>
       <c r="K176" s="5" t="n">
-        <v>49.661776</v>
+        <v>10.87</v>
       </c>
       <c r="L176" s="5" t="n">
-        <v>54.286671</v>
+        <v>14.716</v>
       </c>
       <c r="M176" s="5" t="n">
-        <v>64.736493</v>
-      </c>
-      <c r="N176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9.304</v>
+      </c>
+      <c r="N176" s="5" t="n">
+        <v>10.8</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
@@ -18343,46 +18289,52 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>General and administration (Note 16)</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Transaction costs on derivative warrant liability (Note 12)</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F177" s="5" t="n">
-        <v>0.428256</v>
-      </c>
-      <c r="G177" s="5" t="n">
-        <v>1.684671</v>
-      </c>
-      <c r="H177" s="5" t="n">
-        <v>2.334684</v>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J177" s="5" t="n">
-        <v>2.375</v>
-      </c>
-      <c r="K177" s="5" t="n">
-        <v>6.525</v>
-      </c>
-      <c r="L177" s="5" t="n">
-        <v>7.757</v>
-      </c>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M177" s="5" t="n">
+        <v>0.652</v>
       </c>
       <c r="N177" t="inlineStr">
         <is>
@@ -18408,51 +18360,55 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Research and development (Note 16)</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>ResearchAndDevelopment</t>
-        </is>
-      </c>
+          <t>Change in fair value of warrant derivative (Note 12)</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F178" s="5" t="n">
-        <v>0.771408</v>
-      </c>
-      <c r="G178" s="5" t="n">
-        <v>4.22911</v>
-      </c>
-      <c r="H178" s="5" t="n">
-        <v>5.090146</v>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J178" s="5" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="K178" s="5" t="n">
-        <v>10.87</v>
-      </c>
-      <c r="L178" s="5" t="n">
-        <v>14.716</v>
-      </c>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M178" s="5" t="n">
+        <v>-4.347</v>
+      </c>
+      <c r="N178" s="5" t="n">
+        <v>7.92</v>
       </c>
       <c r="O178" t="inlineStr">
         <is>
@@ -18468,15 +18424,19 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>173      Foreign exchange loss                                                                 208                39</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>173      Foreign exchange loss                                                                 208                39 total</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
+          <t>Foreign exchange loss (gain)</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -18487,39 +18447,37 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G179" s="5" t="n">
+        <v>-0.03413</v>
+      </c>
+      <c r="H179" s="5" t="n">
+        <v>0.043913</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J179" s="5" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="K179" s="5" t="n">
-        <v>-0.106</v>
-      </c>
-      <c r="L179" s="5" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M179" s="5" t="n">
+        <v>-1.646</v>
+      </c>
+      <c r="N179" s="5" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="O179" t="inlineStr">
         <is>
@@ -18535,58 +18493,50 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>(22,640) Comprehensive loss for the year                                                                    (17,303)                (8,186)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share for the year</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F180" s="5" t="n">
+        <v>-1.334064</v>
+      </c>
+      <c r="G180" s="5" t="n">
+        <v>-7.631265</v>
+      </c>
+      <c r="H180" s="5" t="n">
+        <v>-7.465452</v>
+      </c>
+      <c r="I180" s="5" t="n">
+        <v>-4.708031</v>
       </c>
       <c r="J180" s="5" t="n">
-        <v>-2.6e-07</v>
+        <v>-8.276999999999999</v>
       </c>
       <c r="K180" s="5" t="n">
-        <v>-3.5e-07</v>
+        <v>-17.289</v>
       </c>
       <c r="L180" s="5" t="n">
-        <v>-4.2e-07</v>
-      </c>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-22.577</v>
+      </c>
+      <c r="M180" s="5" t="n">
+        <v>-10.048</v>
+      </c>
+      <c r="N180" s="5" t="n">
+        <v>-25.466</v>
       </c>
       <c r="O180" t="inlineStr">
         <is>
@@ -18602,12 +18552,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Weighted average shares</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding (Note 9)</t>
+          <t>Weighted average shares outstanding (Note 9)</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -18625,35 +18575,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G181" s="5" t="n">
-        <v>16.912422</v>
-      </c>
-      <c r="H181" s="5" t="n">
-        <v>24.578137</v>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J181" s="5" t="n">
-        <v>31.89964</v>
-      </c>
-      <c r="K181" s="5" t="n">
-        <v>49.661776</v>
-      </c>
-      <c r="L181" s="5" t="n">
-        <v>54.286671</v>
-      </c>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M181" s="5" t="n">
+        <v>64.736493</v>
+      </c>
+      <c r="N181" s="5" t="n">
+        <v>69.637469</v>
       </c>
       <c r="O181" t="inlineStr">
         <is>
@@ -18674,12 +18630,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Finance income (Note 2d)</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -18687,11 +18643,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F182" s="5" t="n">
-        <v>0.133959</v>
-      </c>
-      <c r="G182" s="5" t="n">
-        <v>-0.03413</v>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -18704,20 +18664,16 @@
         </is>
       </c>
       <c r="J182" s="5" t="n">
-        <v>0.039</v>
+        <v>-0.007</v>
       </c>
       <c r="K182" s="5" t="n">
-        <v>0.208</v>
-      </c>
-      <c r="L182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.314</v>
+      </c>
+      <c r="L182" s="5" t="n">
+        <v>-0.06900000000000001</v>
+      </c>
+      <c r="M182" s="5" t="n">
+        <v>-0.914</v>
       </c>
       <c r="N182" t="inlineStr">
         <is>
@@ -18738,12 +18694,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>(Note 9)</t>
+          <t>Transaction costs on derivative warrant liability</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
@@ -18772,21 +18728,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J183" s="5" t="n">
-        <v>31899.64</v>
-      </c>
-      <c r="K183" s="5" t="n">
-        <v>49661.776</v>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M183" s="5" t="n">
+        <v>0.652</v>
       </c>
       <c r="N183" t="inlineStr">
         <is>
@@ -18812,14 +18770,10 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>General and administration (Note 15)</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Basic and diluted loss per share for the year</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -18836,28 +18790,22 @@
         </is>
       </c>
       <c r="H184" s="5" t="n">
-        <v>2.334684</v>
+        <v>-3.1e-07</v>
       </c>
       <c r="I184" s="5" t="n">
-        <v>1.709286</v>
+        <v>-1.8e-07</v>
       </c>
       <c r="J184" s="5" t="n">
-        <v>2.375211</v>
-      </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.6e-07</v>
+      </c>
+      <c r="K184" s="5" t="n">
+        <v>-3.5e-07</v>
+      </c>
+      <c r="L184" s="5" t="n">
+        <v>-4.2e-07</v>
+      </c>
+      <c r="M184" s="5" t="n">
+        <v>-1.6e-07</v>
       </c>
       <c r="N184" t="inlineStr">
         <is>
@@ -18883,12 +18831,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Research and development (Note 15)</t>
+          <t>Weighted average number of common shares outstanding (Note 9)</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>ResearchAndDevelopment</t>
+          <t>SharesOutstanding</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -18906,29 +18854,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H185" s="5" t="n">
-        <v>5.090146</v>
-      </c>
-      <c r="I185" s="5" t="n">
-        <v>3.017997</v>
-      </c>
-      <c r="J185" s="5" t="n">
-        <v>5.869588</v>
-      </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K185" s="5" t="n">
+        <v>49.661776</v>
+      </c>
+      <c r="L185" s="5" t="n">
+        <v>54.286671</v>
+      </c>
+      <c r="M185" s="5" t="n">
+        <v>64.736493</v>
       </c>
       <c r="N185" t="inlineStr">
         <is>
@@ -18954,39 +18902,41 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Cummulative translation adjustment</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
+          <t>General and administration (Note 16)</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F186" s="5" t="n">
-        <v>0.17696</v>
+        <v>0.428256</v>
       </c>
       <c r="G186" s="5" t="n">
-        <v>0.03727</v>
+        <v>1.684671</v>
       </c>
       <c r="H186" s="5" t="n">
-        <v>-0.063321</v>
-      </c>
-      <c r="I186" s="5" t="n">
-        <v>0.006256</v>
+        <v>2.334684</v>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J186" s="5" t="n">
-        <v>0.09128699999999999</v>
-      </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.375</v>
+      </c>
+      <c r="K186" s="5" t="n">
+        <v>6.525</v>
+      </c>
+      <c r="L186" s="5" t="n">
+        <v>7.757</v>
       </c>
       <c r="M186" t="inlineStr">
         <is>
@@ -19017,12 +18967,12 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding (Note 8(b))</t>
+          <t>Research and development (Note 16)</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>ResearchAndDevelopment</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -19030,36 +18980,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I187" s="5" t="n">
-        <v>25.674027</v>
+      <c r="F187" s="5" t="n">
+        <v>0.771408</v>
+      </c>
+      <c r="G187" s="5" t="n">
+        <v>4.22911</v>
+      </c>
+      <c r="H187" s="5" t="n">
+        <v>5.090146</v>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J187" s="5" t="n">
-        <v>31.89964</v>
-      </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.87</v>
+      </c>
+      <c r="K187" s="5" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="L187" s="5" t="n">
+        <v>14.716</v>
       </c>
       <c r="M187" t="inlineStr">
         <is>
@@ -19085,19 +19027,15 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>173      Foreign exchange loss                                                                 208                39</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>173      Foreign exchange loss                                                                 208                39 total</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -19108,29 +19046,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G188" s="5" t="n">
-        <v>-0.0328</v>
-      </c>
-      <c r="H188" s="5" t="n">
-        <v>-0.003291</v>
-      </c>
-      <c r="I188" s="5" t="n">
-        <v>-0.000102</v>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J188" s="5" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="K188" s="5" t="n">
+        <v>-0.106</v>
+      </c>
+      <c r="L188" s="5" t="n">
+        <v>0.104</v>
       </c>
       <c r="M188" t="inlineStr">
         <is>
@@ -19156,19 +19094,15 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>(22,640) Comprehensive loss for the year                                                                    (17,303)                (8,186)</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding (Note 8(c))</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Basic and diluted loss per share for the year</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -19184,26 +19118,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H189" s="5" t="n">
-        <v>24.367789</v>
-      </c>
-      <c r="I189" s="5" t="n">
-        <v>25.674027</v>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J189" s="5" t="n">
+        <v>-2.6e-07</v>
+      </c>
+      <c r="K189" s="5" t="n">
+        <v>-3.5e-07</v>
+      </c>
+      <c r="L189" s="5" t="n">
+        <v>-4.2e-07</v>
       </c>
       <c r="M189" t="inlineStr">
         <is>
@@ -19229,15 +19161,19 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Listing Expense (Note 5)</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding (Note 9)</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -19249,32 +19185,24 @@
         </is>
       </c>
       <c r="G190" s="5" t="n">
-        <v>1.784414</v>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>16.912422</v>
+      </c>
+      <c r="H190" s="5" t="n">
+        <v>24.578137</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J190" s="5" t="n">
+        <v>31.89964</v>
+      </c>
+      <c r="K190" s="5" t="n">
+        <v>49.661776</v>
+      </c>
+      <c r="L190" s="5" t="n">
+        <v>54.286671</v>
       </c>
       <c r="M190" t="inlineStr">
         <is>
@@ -19305,40 +19233,40 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Interest (income) expense</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr"/>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F191" s="5" t="n">
+        <v>0.133959</v>
       </c>
       <c r="G191" s="5" t="n">
-        <v>-0.0328</v>
-      </c>
-      <c r="H191" s="5" t="n">
-        <v>-0.003291</v>
+        <v>-0.03413</v>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J191" s="5" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="K191" s="5" t="n">
+        <v>0.208</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
@@ -19369,47 +19297,45 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>(Note 9)</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F192" s="5" t="n">
-        <v>-1.157104</v>
-      </c>
-      <c r="G192" s="5" t="n">
-        <v>-7.593995</v>
-      </c>
-      <c r="H192" s="5" t="n">
-        <v>-7.528773</v>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J192" s="5" t="n">
+        <v>31899.64</v>
+      </c>
+      <c r="K192" s="5" t="n">
+        <v>49661.776</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -19445,10 +19371,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Listing expense (Note 5)</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr"/>
+          <t>General and administration (Note 15)</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -19459,23 +19389,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G193" s="5" t="n">
-        <v>1.784414</v>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H193" s="5" t="n">
+        <v>2.334684</v>
+      </c>
+      <c r="I193" s="5" t="n">
+        <v>1.709286</v>
+      </c>
+      <c r="J193" s="5" t="n">
+        <v>2.375211</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
@@ -19516,12 +19442,12 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Interest expense</t>
+          <t>Research and development (Note 15)</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
+          <t>ResearchAndDevelopment</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -19529,26 +19455,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F194" s="5" t="n">
-        <v>0.000441</v>
-      </c>
-      <c r="G194" s="5" t="n">
-        <v>6e-05</v>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H194" s="5" t="n">
+        <v>5.090146</v>
+      </c>
+      <c r="I194" s="5" t="n">
+        <v>3.017997</v>
+      </c>
+      <c r="J194" s="5" t="n">
+        <v>5.869588</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
@@ -19589,61 +19513,1280 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
+          <t>Cummulative translation adjustment</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F195" s="5" t="n">
+        <v>0.17696</v>
+      </c>
+      <c r="G195" s="5" t="n">
+        <v>0.03727</v>
+      </c>
+      <c r="H195" s="5" t="n">
+        <v>-0.063321</v>
+      </c>
+      <c r="I195" s="5" t="n">
+        <v>0.006256</v>
+      </c>
+      <c r="J195" s="5" t="n">
+        <v>0.09128699999999999</v>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding (Note 8(b))</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I196" s="5" t="n">
+        <v>25.674027</v>
+      </c>
+      <c r="J196" s="5" t="n">
+        <v>31.89964</v>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G197" s="5" t="n">
+        <v>-0.0328</v>
+      </c>
+      <c r="H197" s="5" t="n">
+        <v>-0.003291</v>
+      </c>
+      <c r="I197" s="5" t="n">
+        <v>-0.000102</v>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding (Note 8(c))</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H198" s="5" t="n">
+        <v>24.367789</v>
+      </c>
+      <c r="I198" s="5" t="n">
+        <v>25.674027</v>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Listing Expense (Note 5)</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G199" s="5" t="n">
+        <v>1.784414</v>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Interest (income) expense</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G200" s="5" t="n">
+        <v>-0.0328</v>
+      </c>
+      <c r="H200" s="5" t="n">
+        <v>-0.003291</v>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F201" s="5" t="n">
+        <v>-1.157104</v>
+      </c>
+      <c r="G201" s="5" t="n">
+        <v>-7.593995</v>
+      </c>
+      <c r="H201" s="5" t="n">
+        <v>-7.528773</v>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Listing expense (Note 5)</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G202" s="5" t="n">
+        <v>1.784414</v>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F203" s="5" t="n">
+        <v>0.000441</v>
+      </c>
+      <c r="G203" s="5" t="n">
+        <v>6e-05</v>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
           <t>Weighted average number of common shares outstanding (note 9(d))</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr">
+      <c r="D204" t="inlineStr">
         <is>
           <t>SharesOutstanding</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F195" s="5" t="n">
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F204" s="5" t="n">
         <v>15.996038</v>
       </c>
-      <c r="G195" s="5" t="n">
+      <c r="G204" s="5" t="n">
         <v>16.912422</v>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O195" t="inlineStr">
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Expenses relating to identification of Qualifying Transaction $</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" s="5" t="n">
+        <v>0.016914</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Stock based compensation (Note 9(b))</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" s="5" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E207" s="5" t="n">
+        <v>0.01935</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Office and administrative</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E208" s="5" t="n">
+        <v>0.031418</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E209" s="5" t="n">
+        <v>0.202682</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the period $</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E210" s="5" t="n">
+        <v>-0.202682</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Net loss per common share</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Basic and fully diluted (Note 10) $</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" s="5" t="n">
+        <v>8e-08</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Basic and fully diluted (Note 10)</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" s="5" t="n">
+        <v>2.665663</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
         <is>
           <t>-</t>
         </is>
